--- a/assets/constructions/examples/ctd_tko_thread.xlsx
+++ b/assets/constructions/examples/ctd_tko_thread.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,11 +649,36 @@
           <t>thr_id</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VE11TH 19BSPT RVTX</t>
+          <t>VE11TH 19W LVTX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -700,7 +725,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2A/2B</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -715,19 +740,19 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>NPT60</t>
+          <t>WH55</t>
         </is>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.35</v>
+        <v>12.7</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -773,11 +798,30 @@
         </is>
       </c>
       <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>2544.72</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V14THAG60RVTX</t>
+          <t>V08TH16UNRVBX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -792,7 +836,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>V14</t>
+          <t>V08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -808,63 +852,61 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>4.33</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>60</v>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0.92</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>F</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>IT 6</t>
+          <t>2A/2B</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X3" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35</v>
+        <v>0.92</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>VP60</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
@@ -874,7 +916,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>VARGUS_V14</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -884,17 +926,17 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>V14</t>
+          <t>V08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -919,11 +961,22 @@
         </is>
       </c>
       <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VE08TH 14UN RVTX</t>
+          <t>V08TH3.0TRRVBX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -936,8 +989,16 @@
           <t>Mini-V</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -949,22 +1010,32 @@
         <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.78</v>
+        <v>4.95</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>30</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.75</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>F</t>
@@ -972,29 +1043,25 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2A/2B</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>14</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
+          <t>7e/7H</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>TP30</t>
         </is>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.113</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
@@ -1014,15 +1081,19 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+          <t>TiCN</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -1041,15 +1112,26 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2021/Groovex Vargus</t>
+          <t>2019 / Groovex Catalog</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V14THA55RVBX</t>
+          <t>VE08TH .75ISO RVTX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1062,16 +1144,8 @@
           <t>Mini-V</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>V14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -1080,63 +1154,53 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>4.19</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>55</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>F</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>IT 6</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>16</v>
-      </c>
-      <c r="X5" t="n">
-        <v>48</v>
-      </c>
+          <t>6H</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>1.71</v>
+        <v>0.43</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>VP55</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>8.5</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
@@ -1146,7 +1210,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>VARGUS_V14</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1156,19 +1220,15 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>TiCN</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>V14</t>
-        </is>
-      </c>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -1187,15 +1247,34 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>2021/Groovex Vargus</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>2526.34</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V14THAG55RVTX</t>
+          <t>VE08TH 16UN LVTX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1208,16 +1287,8 @@
           <t>Mini-V</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>V14</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -1226,73 +1297,65 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>4.33</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>55</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>F</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>IT 6</t>
+          <t>2A/2B</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X6" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.7</v>
+        <v>0.92</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>VP55</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="AB6" t="n">
         <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>9.525</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>VARGUS_V14</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1310,11 +1373,7 @@
           <t>TiAlN</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>V14</t>
-        </is>
-      </c>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -1333,10 +1392,29 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>2021/Groovex Vargus</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>2526.34</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
